--- a/python-excel-arima-demo.xlsx
+++ b/python-excel-arima-demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2000001_{E3306693-8907-48C6-B2DC-5AC57E3AB296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD8C5F6-C6F5-4B0B-A9A6-241F764387EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,7 +243,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -389,10 +389,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="\$0.00"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -436,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -446,6 +447,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,16 +469,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>376768</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>160867</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>542985</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>348252</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>42334</xdr:rowOff>
+      <xdr:rowOff>29634</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -504,7 +506,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3310468" y="4165600"/>
+          <a:off x="4385735" y="4152900"/>
           <a:ext cx="3273484" cy="1951567"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -516,16 +518,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>182035</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>50799</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>605368</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>215902</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>136200</xdr:rowOff>
+      <xdr:rowOff>13433</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -553,7 +555,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3310468" y="6595533"/>
+          <a:off x="4191002" y="6472766"/>
           <a:ext cx="4013200" cy="2392567"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -565,16 +567,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>59267</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>4234</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>385234</xdr:colOff>
+      <xdr:colOff>550333</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>166577</xdr:rowOff>
+      <xdr:rowOff>170811</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -602,7 +604,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3310468" y="9372600"/>
+          <a:off x="4068234" y="9376834"/>
           <a:ext cx="3793066" cy="2249377"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -614,16 +616,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>118535</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>249767</xdr:colOff>
+      <xdr:colOff>474135</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>21756</xdr:rowOff>
+      <xdr:rowOff>123356</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -651,7 +653,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3310468" y="11802533"/>
+          <a:off x="4127502" y="11904133"/>
           <a:ext cx="5012266" cy="2972390"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1152,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J521"/>
+  <dimension ref="A1:L521"/>
   <sheetFormatPr defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="9.94140625" bestFit="1" customWidth="1"/>
@@ -1160,6 +1162,11 @@
     <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="7"/>
+    <col min="8" max="8" width="12.38671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1275,16 +1282,16 @@
         <f t="array" ref="F7:J12">_xlfn._xlws.PY(3,0)</f>
         <v/>
       </c>
-      <c r="G7" t="str">
+      <c r="G7" s="7" t="str">
         <v>forecast</v>
       </c>
-      <c r="H7" t="str">
+      <c r="H7" s="7" t="str">
         <v>standard_error</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I7" s="7" t="str">
         <v>lower_bound</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J7" s="7" t="str">
         <v>upper_bound</v>
       </c>
     </row>
@@ -1304,16 +1311,16 @@
       <c r="F8" vm="4">
         <v>43466</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="7">
         <v>0.19247074050701118</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="7">
         <v>1.8724559538482198E-2</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="7">
         <v>0.15577127818521014</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="7">
         <v>0.22917020282881223</v>
       </c>
     </row>
@@ -1333,16 +1340,16 @@
       <c r="F9" vm="5">
         <v>43467</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="7">
         <v>0.19286190583396703</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="7">
         <v>2.291762439978981E-2</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="7">
         <v>0.14794418739916262</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="7">
         <v>0.23777962426877144</v>
       </c>
     </row>
@@ -1362,16 +1369,16 @@
       <c r="F10" vm="6">
         <v>43468</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="7">
         <v>0.19161638401733153</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="7">
         <v>2.5044751531392302E-2</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="7">
         <v>0.14252957301404826</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="7">
         <v>0.2407031950206148</v>
       </c>
     </row>
@@ -1391,16 +1398,16 @@
       <c r="F11" vm="7">
         <v>43469</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="7">
         <v>0.19217886397321629</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="7">
         <v>2.6367404889758396E-2</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="7">
         <v>0.14049970002350454</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="7">
         <v>0.24385802792292804</v>
       </c>
     </row>
@@ -1420,16 +1427,16 @@
       <c r="F12" vm="8">
         <v>43472</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="7">
         <v>0.19202603268436205</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="7">
         <v>2.7272444754931027E-2</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="7">
         <v>0.13857302319433895</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="7">
         <v>0.24547904217438515</v>
       </c>
     </row>
@@ -1510,7 +1517,7 @@
         <f t="array" ref="F17:G23">_xlfn._xlws.PY(5,0)</f>
         <v/>
       </c>
-      <c r="G17" t="str">
+      <c r="G17" s="7" t="str">
         <v>fitted</v>
       </c>
     </row>
@@ -1530,7 +1537,7 @@
       <c r="F18" t="str">
         <v>date</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G18" s="7" t="str">
         <v/>
       </c>
     </row>
@@ -1550,7 +1557,7 @@
       <c r="F19" vm="10">
         <v>42738</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="7">
         <v>0.1949327571836228</v>
       </c>
     </row>
@@ -1570,7 +1577,7 @@
       <c r="F20" vm="11">
         <v>42739</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="7">
         <v>0.18116142608053884</v>
       </c>
     </row>
@@ -1590,7 +1597,7 @@
       <c r="F21" vm="12">
         <v>42740</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="7">
         <v>0.17783930564218725</v>
       </c>
     </row>
@@ -1610,7 +1617,7 @@
       <c r="F22" vm="13">
         <v>42741</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="7">
         <v>0.17005311677779558</v>
       </c>
     </row>
@@ -1630,7 +1637,7 @@
       <c r="F23" vm="14">
         <v>42744</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="7">
         <v>0.17317808894013023</v>
       </c>
     </row>

--- a/python-excel-arima-demo.xlsx
+++ b/python-excel-arima-demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD8C5F6-C6F5-4B0B-A9A6-241F764387EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28F1D35-0EFF-4180-A48F-9CFC8E844A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -469,16 +469,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>376768</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>21169</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>160867</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>348252</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>29634</xdr:rowOff>
+      <xdr:colOff>622008</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>105833</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -506,8 +506,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4385735" y="4152900"/>
-          <a:ext cx="3273484" cy="1951567"/>
+          <a:off x="3331636" y="4131733"/>
+          <a:ext cx="4601339" cy="2743200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -518,16 +518,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>182035</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>50799</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>16936</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>4232</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>215902</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>13433</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>617774</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>143932</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -555,8 +555,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4191002" y="6472766"/>
-          <a:ext cx="4013200" cy="2392567"/>
+          <a:off x="3327403" y="6946899"/>
+          <a:ext cx="4601338" cy="2743200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -567,16 +567,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>59267</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>4234</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>8466</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>151908</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>550333</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>170811</xdr:rowOff>
+      <xdr:colOff>633752</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>118042</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -604,8 +604,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4068234" y="9376834"/>
-          <a:ext cx="3793066" cy="2249377"/>
+          <a:off x="3318933" y="9698075"/>
+          <a:ext cx="4625786" cy="2743200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -616,16 +616,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>118535</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>660403</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>474135</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123356</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>608358</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>118533</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -653,8 +653,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4127502" y="11904133"/>
-          <a:ext cx="5012266" cy="2972390"/>
+          <a:off x="3293536" y="12475633"/>
+          <a:ext cx="4625789" cy="2743200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
